--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:55:35+00:00</t>
+    <t>2026-09-16T07:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T07:37:42+00:00</t>
+    <t>2026-09-17T12:36:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -543,7 +543,7 @@
     <t>accessionNumber</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-accession-number-identifier|2.2.0}
+    <t xml:space="preserve">Identifier {http://hl7.eu/fhir/imaging/StructureDefinition/AccessionNumberIdentifierEuImaging|1.0.0-ballot}
 </t>
   </si>
   <si>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:36:37+00:00</t>
+    <t>2026-09-17T13:03:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
+++ b/nr-doc-core-service-request/ig/StructureDefinition-fr-core-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:03:48+00:00</t>
+    <t>2026-10-13T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
